--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260708.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>909,044,000</t>
+          <t>915,244,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.55%</t>
+          <t>10.65%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>169,841,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.41%</t>
+          <t>10.45%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>6.00%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.93%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.32%</t>
         </is>
       </c>
     </row>
@@ -726,73 +726,73 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,005,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>5,005,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -814,117 +814,117 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>25,944,000</t>
+          <t>31,536,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>31,256,000</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>25,944,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -946,29 +946,29 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>150,152,000</t>
+          <t>1,670</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -985,100 +985,100 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>133,147,000</t>
+          <t>134,528,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,696</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>371,675,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>371,675,000</t>
+          <t>101,917,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>100,847,000</t>
+          <t>150,152,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1100,139 +1100,139 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>82,168,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>82,168,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>281,366,000</t>
+          <t>179,956,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>178,956,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,683,000</t>
+          <t>281,366,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>14,683,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,628,447,680</t>
+          <t>10,876,151,059</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,270,528,792</t>
+          <t>3,225,656,085</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-66,515,215</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
